--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6905410</v>
+        <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>106401</v>
+        <v>110404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1885</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klockgentiana</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentiana pneumonanthe</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,35 +708,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Husaby, Bolmsö, Sm</t>
+          <t>Väg 560, Stapaled, Bolmsö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420959</v>
+        <v>423301</v>
       </c>
       <c r="R2" t="n">
-        <v>6309918</v>
+        <v>6310516</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3+3 blommor</t>
+          <t>Väster om vägen i bankslänten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,35 +768,31 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Sand/grusstrand i näringsfattig sjö</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6905410</t>
+          <t>https://artportalen.se/Sighting/137366804</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6905412</v>
+        <v>6905410</v>
       </c>
       <c r="B3" t="n">
         <v>106401</v>
@@ -837,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420934</v>
+        <v>420959</v>
       </c>
       <c r="R3" t="n">
-        <v>6309989</v>
+        <v>6309918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>7 plantor med 1 blomma, 6 plantor med 2, 1 planta med 3, 3 plantor med 4, 2 plantor med 5 och 2 plantor med 8 blommor</t>
+          <t>3+3 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,43 +913,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6905412</t>
+          <t>https://artportalen.se/Sighting/6905410</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6905408</v>
+        <v>6905412</v>
       </c>
       <c r="B4" t="n">
-        <v>100475</v>
+        <v>106401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>522</v>
+        <v>1885</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sjötåtel</t>
+          <t>Klockgentiana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Deschampsia setacea</t>
+          <t>Gentiana pneumonanthe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huds.) Hack.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,7 +959,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -984,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420969</v>
+        <v>420934</v>
       </c>
       <c r="R4" t="n">
-        <v>6309608</v>
+        <v>6309989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,6 +1007,11 @@
           <t>2013-08-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7 plantor med 1 blomma, 6 plantor med 2, 1 planta med 3, 3 plantor med 4, 2 plantor med 5 och 2 plantor med 8 blommor</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1050,43 +1040,43 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6905408</t>
+          <t>https://artportalen.se/Sighting/6905412</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6905405</v>
+        <v>6905408</v>
       </c>
       <c r="B5" t="n">
-        <v>106401</v>
+        <v>100475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1885</v>
+        <v>522</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klockgentiana</t>
+          <t>Sjötåtel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gentiana pneumonanthe</t>
+          <t>Deschampsia setacea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huds.) Hack.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1096,20 +1086,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Almesand, Bolmsö, Sm</t>
+          <t>Husaby, Bolmsö, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420910</v>
+        <v>420969</v>
       </c>
       <c r="R5" t="n">
-        <v>6309399</v>
+        <v>6309608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,11 +1134,6 @@
           <t>2013-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>16 plantor med 1 blomma, 12 plantor med 2, 2plantor med 3, 1 planta med 4, 4 plantor med 5, 1 planta med 6 och 1 planta med 10 blommor</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1176,6 +1161,133 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6905408</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6905405</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106401</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klockgentiana</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gentiana pneumonanthe</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Almesand, Bolmsö, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>420910</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6309399</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bolmsö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-08-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-08-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>16 plantor med 1 blomma, 12 plantor med 2, 2plantor med 3, 1 planta med 4, 4 plantor med 5, 1 planta med 6 och 1 planta med 10 blommor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sand/grusstrand i näringsfattig sjö</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6905405</t>
         </is>
@@ -1187,6 +1299,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1526-2023 artfynd.xlsx
+++ b/artfynd/S 1526-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137366804</v>
       </c>
       <c r="B2" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
